--- a/output/graficos_dimensiones/comunal_d_env_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:14</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_la araucania.xlsx
@@ -54,12 +54,12 @@
     <t xml:space="preserve">Teodoro Schmidt</t>
   </si>
   <si>
+    <t xml:space="preserve">Freire</t>
+  </si>
+  <si>
     <t xml:space="preserve">Los Sauces</t>
   </si>
   <si>
-    <t xml:space="preserve">Freire</t>
-  </si>
-  <si>
     <t xml:space="preserve">Victoria</t>
   </si>
   <si>
@@ -90,12 +90,12 @@
     <t xml:space="preserve">Perquenco</t>
   </si>
   <si>
+    <t xml:space="preserve">Galvarino</t>
+  </si>
+  <si>
     <t xml:space="preserve">Angol</t>
   </si>
   <si>
-    <t xml:space="preserve">Galvarino</t>
-  </si>
-  <si>
     <t xml:space="preserve">Renaico</t>
   </si>
   <si>
@@ -105,24 +105,24 @@
     <t xml:space="preserve">Curarrehue</t>
   </si>
   <si>
+    <t xml:space="preserve">Collipulli</t>
+  </si>
+  <si>
     <t xml:space="preserve">Temuco</t>
   </si>
   <si>
-    <t xml:space="preserve">Collipulli</t>
-  </si>
-  <si>
     <t xml:space="preserve">Villarrica</t>
   </si>
   <si>
     <t xml:space="preserve">Vilcún</t>
   </si>
   <si>
+    <t xml:space="preserve">Cholchol</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lautaro</t>
   </si>
   <si>
-    <t xml:space="preserve">Cholchol</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ercilla</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -574,7 +574,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>119.82</v>
+        <v>129.34</v>
       </c>
     </row>
     <row r="3">
@@ -591,7 +591,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>117.4</v>
+        <v>125.34</v>
       </c>
     </row>
     <row r="4">
@@ -608,7 +608,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>117.02</v>
+        <v>124.67</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>113.76</v>
+        <v>121.44</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>109.88</v>
+        <v>119.45</v>
       </c>
     </row>
     <row r="7">
@@ -659,7 +659,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>109.87</v>
+        <v>118.61</v>
       </c>
     </row>
     <row r="8">
@@ -670,13 +670,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>9206</v>
+        <v>9105</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>108.51</v>
+        <v>117.65</v>
       </c>
     </row>
     <row r="9">
@@ -687,13 +687,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>9105</v>
+        <v>9206</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>107.68</v>
+        <v>116.7</v>
       </c>
     </row>
     <row r="10">
@@ -710,7 +710,7 @@
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>103.41</v>
+        <v>111.39</v>
       </c>
     </row>
     <row r="11">
@@ -727,7 +727,7 @@
         <v>2018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>103.01</v>
+        <v>110.96</v>
       </c>
     </row>
     <row r="12">
@@ -744,7 +744,7 @@
         <v>2018</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>102.82</v>
+        <v>110.46</v>
       </c>
     </row>
     <row r="13">
@@ -761,7 +761,7 @@
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>101.71</v>
+        <v>108.56</v>
       </c>
     </row>
     <row r="14">
@@ -778,7 +778,7 @@
         <v>2018</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>99.86</v>
+        <v>106.81</v>
       </c>
     </row>
     <row r="15">
@@ -795,7 +795,7 @@
         <v>2018</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>99.44</v>
+        <v>106.64</v>
       </c>
     </row>
     <row r="16">
@@ -812,7 +812,7 @@
         <v>2018</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>95.42</v>
+        <v>101.76</v>
       </c>
     </row>
     <row r="17">
@@ -829,7 +829,7 @@
         <v>2018</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>94.32</v>
+        <v>101.62</v>
       </c>
     </row>
     <row r="18">
@@ -846,7 +846,7 @@
         <v>2018</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>92.78</v>
+        <v>98.49</v>
       </c>
     </row>
     <row r="19">
@@ -863,7 +863,7 @@
         <v>2018</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>88.1</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20">
@@ -874,13 +874,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>9201</v>
+        <v>9106</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>86.71</v>
+        <v>93.02</v>
       </c>
     </row>
     <row r="21">
@@ -891,13 +891,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>9106</v>
+        <v>9201</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>86.14</v>
+        <v>92.58</v>
       </c>
     </row>
     <row r="22">
@@ -914,7 +914,7 @@
         <v>2018</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>83.3</v>
+        <v>89.14</v>
       </c>
     </row>
     <row r="23">
@@ -931,7 +931,7 @@
         <v>2018</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>81.99</v>
+        <v>87.93</v>
       </c>
     </row>
     <row r="24">
@@ -948,7 +948,7 @@
         <v>2018</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>80.96</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="25">
@@ -959,13 +959,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>9101</v>
+        <v>9202</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>80.29</v>
+        <v>86.17</v>
       </c>
     </row>
     <row r="26">
@@ -976,13 +976,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>9202</v>
+        <v>9101</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>80.18</v>
+        <v>86.01</v>
       </c>
     </row>
     <row r="27">
@@ -999,7 +999,7 @@
         <v>2018</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>79.13</v>
+        <v>84.54</v>
       </c>
     </row>
     <row r="28">
@@ -1016,7 +1016,7 @@
         <v>2018</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>78.01</v>
+        <v>83.47</v>
       </c>
     </row>
     <row r="29">
@@ -1027,13 +1027,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>9108</v>
+        <v>9121</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>76.3</v>
+        <v>81.91</v>
       </c>
     </row>
     <row r="30">
@@ -1044,13 +1044,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>9121</v>
+        <v>9108</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>75.98</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="31">
@@ -1067,7 +1067,7 @@
         <v>2018</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>72.8</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="32">
@@ -1084,7 +1084,7 @@
         <v>2018</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>67.9</v>
+        <v>72.77</v>
       </c>
     </row>
     <row r="33">
@@ -1101,7 +1101,7 @@
         <v>2018</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>67.72</v>
+        <v>72.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:40</t>
+    <t xml:space="preserve">2026-10-05 16:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
